--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_349_R35.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_349_R35.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. AJINCA</t>
+          <t>T. HEURTEL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,58 +565,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.388</v>
+        <v>2.9311</v>
       </c>
       <c r="E2" t="n">
-        <v>1.322</v>
+        <v>1.9166</v>
       </c>
       <c r="F2" t="n">
-        <v>1.066</v>
+        <v>1.0145</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9925</v>
+        <v>3.3152</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3627</v>
+        <v>-1.0444</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6297</v>
+        <v>4.3597</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4852</v>
+        <v>3.9488</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.8472</v>
       </c>
       <c r="L2" t="n">
-        <v>1.8467</v>
+        <v>3.1015</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5072</v>
+        <v>-0.6335</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2759</v>
+        <v>-1.8917</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7831</v>
+        <v>1.2582</v>
       </c>
       <c r="P2" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R2" t="n">
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8364</v>
+        <v>-0.8481</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2284</v>
+        <v>-0.8725000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0649</v>
+        <v>0.0244</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. HEURTEL</t>
+          <t>M. AJINCA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0821</v>
+        <v>2.4284</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3701</v>
+        <v>1.1607</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7121</v>
+        <v>1.2677</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3152</v>
+        <v>2.9925</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.0444</v>
+        <v>0.3627</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3597</v>
+        <v>2.6297</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9488</v>
+        <v>2.4852</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8472</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>3.1015</v>
+        <v>1.8467</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6335</v>
+        <v>0.5072</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.8917</v>
+        <v>-0.2759</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2582</v>
+        <v>0.7831</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R3" t="n">
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.697</v>
+        <v>-0.796</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.4189</v>
+        <v>0.0672</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2781</v>
+        <v>-0.8632</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0194</v>
+        <v>1.2023</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.7105</v>
+        <v>-1.5611</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7299</v>
+        <v>2.7635</v>
       </c>
       <c r="G4" t="n">
         <v>0.8372000000000001</v>
@@ -766,13 +766,13 @@
         <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6012</v>
+        <v>-1.4183</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.4832</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9686</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5361</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.138</v>
+        <v>1.1638</v>
       </c>
       <c r="E5" t="n">
-        <v>0.094</v>
+        <v>1.187</v>
       </c>
       <c r="F5" t="n">
-        <v>0.044</v>
+        <v>-0.0232</v>
       </c>
       <c r="G5" t="n">
         <v>1.1547</v>
@@ -844,13 +844,13 @@
         <v>2.5515</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.5374</v>
+        <v>-1.5116</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1949</v>
+        <v>-0.1019</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.3425</v>
+        <v>-1.4097</v>
       </c>
       <c r="V5" t="n">
         <v>2.6805</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6097</v>
+        <v>-0.3065</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5205</v>
+        <v>-0.2846</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0892</v>
+        <v>-0.022</v>
       </c>
       <c r="G6" t="n">
         <v>-0.969</v>
@@ -922,13 +922,13 @@
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8004</v>
+        <v>-0.4973</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3734</v>
+        <v>-0.1375</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.427</v>
+        <v>-0.3598</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Z. SELJAAS</t>
+          <t>S. HARRISON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.023</v>
+        <v>-0.5107</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4507</v>
+        <v>-0.653</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4737</v>
+        <v>0.1423</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4054</v>
+        <v>0.018</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.08749999999999999</v>
+        <v>0.4128</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3179</v>
+        <v>-0.3948</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8628</v>
+        <v>1.0332</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1344</v>
+        <v>0.5314</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.9973</v>
+        <v>0.5018</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4574</v>
+        <v>-1.0152</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.222</v>
+        <v>-0.1186</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6793</v>
+        <v>-0.8966</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1171</v>
+        <v>-1.2246</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3135</v>
+        <v>-0.2946</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1964</v>
+        <v>-0.93</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.3584</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.3584</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2736</v>
+        <v>-1.1242</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9226</v>
+        <v>-0.7733</v>
       </c>
       <c r="F8" t="n">
         <v>-0.3509</v>
@@ -1078,10 +1078,10 @@
         <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0984</v>
+        <v>0.2478</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1098</v>
+        <v>0.0395</v>
       </c>
       <c r="U8" t="n">
         <v>0.2082</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. HARRISON</t>
+          <t>Z. SELJAAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5529</v>
+        <v>-1.5985</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.628</v>
+        <v>-0.2256</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0751</v>
+        <v>-1.3729</v>
       </c>
       <c r="G9" t="n">
-        <v>0.018</v>
+        <v>-0.4054</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4128</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3948</v>
+        <v>-0.3179</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0332</v>
+        <v>-0.8628</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5314</v>
+        <v>0.1344</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5018</v>
+        <v>-0.9973</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0152</v>
+        <v>0.4574</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1186</v>
+        <v>-0.222</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8966</v>
+        <v>0.6793</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.2668</v>
+        <v>0.5417</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2696</v>
+        <v>0.6372</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9972</v>
+        <v>-0.0955</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-3.3584</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-3.3584</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6998</v>
+        <v>-1.7095</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4021</v>
+        <v>0.3589</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1019</v>
+        <v>-2.0683</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7020999999999999</v>
@@ -1234,13 +1234,13 @@
         <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1032</v>
+        <v>-0.1129</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1889</v>
+        <v>0.1456</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2921</v>
+        <v>-0.2585</v>
       </c>
       <c r="V10" t="n">
         <v>-2.2862</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7981</v>
+        <v>-1.8921</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3401</v>
+        <v>-3.5013</v>
       </c>
       <c r="F11" t="n">
-        <v>1.542</v>
+        <v>1.6092</v>
       </c>
       <c r="G11" t="n">
         <v>-0.8562</v>
@@ -1312,13 +1312,13 @@
         <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0141</v>
+        <v>-0.1081</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1098</v>
+        <v>-0.2711</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0958</v>
+        <v>0.163</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5445</v>
+        <v>-3.766</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6268</v>
+        <v>-3.3777</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0822</v>
+        <v>-0.3883</v>
       </c>
       <c r="G12" t="n">
         <v>-2.0862</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9875</v>
+        <v>-0.2339</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7512</v>
+        <v>0.0002</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2364</v>
+        <v>-0.2341</v>
       </c>
       <c r="V12" t="n">
         <v>-1.214</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.7754</v>
+        <v>-4.3473</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2324</v>
+        <v>-2.4683</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.543</v>
+        <v>-1.879</v>
       </c>
       <c r="G13" t="n">
         <v>-3.0225</v>
@@ -1468,13 +1468,13 @@
         <v>0.232</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0668</v>
+        <v>-0.5052</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1142</v>
+        <v>-0.1217</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0474</v>
+        <v>-0.3835</v>
       </c>
       <c r="V13" t="n">
         <v>-0.8197</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.6495</v>
+        <v>-7.5292</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.341999999999999</v>
+        <v>-8.2217</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6926000000000003</v>
+        <v>0.6926000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>-1.809599999999997</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.773800000000001</v>
+        <v>-5.7738</v>
       </c>
       <c r="I14" t="n">
         <v>3.964499999999999</v>
@@ -1528,7 +1528,7 @@
         <v>2.4243</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.683399999999999</v>
+        <v>-2.6834</v>
       </c>
       <c r="N14" t="n">
         <v>-4.2236</v>
@@ -1546,13 +1546,13 @@
         <v>18.5564</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.5867</v>
+        <v>-6.466500000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.5128</v>
+        <v>-1.3928</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.073799999999999</v>
+        <v>-5.073699999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-6.211799999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.5017</v>
+        <v>5.9462</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9951</v>
+        <v>4.6412</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5066</v>
+        <v>1.305</v>
       </c>
       <c r="G15" t="n">
         <v>2.2835</v>
@@ -1624,13 +1624,13 @@
         <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9294</v>
+        <v>1.3739</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2819</v>
+        <v>0.928</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6475</v>
+        <v>0.4459</v>
       </c>
       <c r="V15" t="n">
         <v>3.2166</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.8727</v>
+        <v>2.8854</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8956</v>
+        <v>1.2443</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9771</v>
+        <v>1.6411</v>
       </c>
       <c r="G16" t="n">
         <v>0.0427</v>
@@ -1702,13 +1702,13 @@
         <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>3.0979</v>
+        <v>1.1106</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4065</v>
+        <v>0.7551</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6915</v>
+        <v>0.3554</v>
       </c>
       <c r="V16" t="n">
         <v>2.428</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.184</v>
+        <v>2.7965</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4915</v>
+        <v>2.1376</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6925</v>
+        <v>0.6589</v>
       </c>
       <c r="G17" t="n">
         <v>-1.0976</v>
@@ -1780,13 +1780,13 @@
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>2.1398</v>
+        <v>1.7524</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3882</v>
+        <v>1.0343</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7517</v>
+        <v>0.718</v>
       </c>
       <c r="V17" t="n">
         <v>1.214</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.3839</v>
+        <v>2.233</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4201</v>
+        <v>0.538</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9639</v>
+        <v>1.695</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2246</v>
@@ -1858,13 +1858,13 @@
         <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3945</v>
+        <v>0.2436</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1336</v>
+        <v>-0.0156</v>
       </c>
       <c r="U18" t="n">
-        <v>0.528</v>
+        <v>0.2592</v>
       </c>
       <c r="V18" t="n">
         <v>1.7501</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. WARD</t>
+          <t>T. DORSEY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.0939</v>
+        <v>1.3919</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3772</v>
+        <v>0.1852</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7166</v>
+        <v>1.2067</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4989</v>
+        <v>3.1883</v>
       </c>
       <c r="H19" t="n">
-        <v>2.3587</v>
+        <v>0.2774</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8598</v>
+        <v>2.9109</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9561</v>
+        <v>2.3234</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9193</v>
+        <v>0.3529</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0368</v>
+        <v>1.9705</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4572</v>
+        <v>0.8649</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4395</v>
+        <v>-0.0755</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8966</v>
+        <v>0.9403</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9278</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3195</v>
+        <v>-2.5515</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>1.9171</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>2.135</v>
+        <v>0.2715</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2179</v>
+        <v>-0.3541</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3943</v>
+        <v>0.1418</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3943</v>
+        <v>0.1418</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. DORSEY</t>
+          <t>T. WARD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9886</v>
+        <v>1.3012</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1852</v>
+        <v>0.3157</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8034</v>
+        <v>0.9855</v>
       </c>
       <c r="G20" t="n">
-        <v>3.1883</v>
+        <v>1.4989</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2774</v>
+        <v>2.3587</v>
       </c>
       <c r="I20" t="n">
-        <v>2.9109</v>
+        <v>-0.8598</v>
       </c>
       <c r="J20" t="n">
-        <v>2.3234</v>
+        <v>1.9561</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3529</v>
+        <v>1.9193</v>
       </c>
       <c r="L20" t="n">
-        <v>1.9705</v>
+        <v>0.0368</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8649</v>
+        <v>-0.4572</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0755</v>
+        <v>0.4395</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9403</v>
+        <v>-0.8966</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.8556</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.5515</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4859</v>
+        <v>1.1244</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2715</v>
+        <v>1.0734</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7573</v>
+        <v>0.051</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1418</v>
+        <v>-0.3943</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1418</v>
+        <v>-0.3943</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3444</v>
+        <v>0.8835</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1702</v>
+        <v>-1.6984</v>
       </c>
       <c r="F21" t="n">
-        <v>2.5147</v>
+        <v>2.5819</v>
       </c>
       <c r="G21" t="n">
         <v>3.1768</v>
@@ -2092,13 +2092,13 @@
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4586</v>
+        <v>0.0804</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4402</v>
+        <v>0.0316</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0184</v>
+        <v>0.0488</v>
       </c>
       <c r="V21" t="n">
         <v>-1.214</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. PETERS</t>
+          <t>E. FOURNIER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.613</v>
+        <v>-1.5794</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2731</v>
+        <v>-1.6549</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6601</v>
+        <v>0.0755</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.5285</v>
+        <v>-2.3607</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7467</v>
+        <v>-1.3301</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.2753</v>
+        <v>-1.0305</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1963</v>
+        <v>-0.6919</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1259</v>
+        <v>-1.4012</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.3222</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3322</v>
+        <v>-1.6687</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3792</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>0.047</v>
+        <v>-1.7398</v>
       </c>
       <c r="P22" t="n">
         <v>-0.232</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0057</v>
+        <v>1.0132</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0589</v>
+        <v>0.4288</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0646</v>
+        <v>0.5845</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. FOURNIER</t>
+          <t>A. PETERS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4894</v>
+        <v>-1.6631</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5985</v>
+        <v>-2.1552</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1091</v>
+        <v>0.4921</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.3607</v>
+        <v>-1.5285</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3301</v>
+        <v>0.7467</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0305</v>
+        <v>-2.2753</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6919</v>
+        <v>-1.1963</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.4012</v>
+        <v>1.1259</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7092000000000001</v>
+        <v>-2.3222</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6687</v>
+        <v>-0.3322</v>
       </c>
       <c r="N23" t="n">
-        <v>0.07099999999999999</v>
+        <v>-0.3792</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.7398</v>
+        <v>0.047</v>
       </c>
       <c r="P23" t="n">
         <v>-0.232</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1032</v>
+        <v>-0.0444</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5149</v>
+        <v>0.0591</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6181</v>
+        <v>-0.1034</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2879</v>
+        <v>-1.9911</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.7361</v>
+        <v>-0.6745</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5518</v>
+        <v>-1.3166</v>
       </c>
       <c r="G24" t="n">
         <v>-2.285</v>
@@ -2326,13 +2326,13 @@
         <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.539</v>
+        <v>0.7578</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5895</v>
+        <v>0.472</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0505</v>
+        <v>0.2858</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.3295</v>
+        <v>-3.5546</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.2793</v>
+        <v>-3.5716</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0502</v>
+        <v>0.017</v>
       </c>
       <c r="G25" t="n">
         <v>-0.8842</v>
@@ -2404,13 +2404,13 @@
         <v>0.6959</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5175</v>
+        <v>0.2574</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6721</v>
+        <v>0.0356</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1546</v>
+        <v>0.2219</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0722</v>
@@ -2437,34 +2437,34 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>8.6494</v>
+        <v>8.6495</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.6925000000000012</v>
+        <v>-0.6925999999999997</v>
       </c>
       <c r="F26" t="n">
-        <v>9.342000000000001</v>
+        <v>9.342100000000002</v>
       </c>
       <c r="G26" t="n">
         <v>1.8096</v>
       </c>
       <c r="H26" t="n">
-        <v>5.774</v>
+        <v>5.773999999999999</v>
       </c>
       <c r="I26" t="n">
         <v>-3.9643</v>
       </c>
       <c r="J26" t="n">
-        <v>2.6834</v>
+        <v>2.683399999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>4.223399999999999</v>
+        <v>4.2234</v>
       </c>
       <c r="L26" t="n">
         <v>-1.5401</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.8737999999999995</v>
+        <v>-0.8737999999999999</v>
       </c>
       <c r="N26" t="n">
         <v>1.5505</v>
@@ -2482,13 +2482,13 @@
         <v>11.5978</v>
       </c>
       <c r="S26" t="n">
-        <v>7.586599999999999</v>
+        <v>7.5867</v>
       </c>
       <c r="T26" t="n">
-        <v>5.073899999999999</v>
+        <v>5.073799999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>2.5129</v>
+        <v>2.513</v>
       </c>
       <c r="V26" t="n">
         <v>6.2118</v>
